--- a/development/service-ops-api/src/main/resources/templates/excel/riders-template.xlsx
+++ b/development/service-ops-api/src/main/resources/templates/excel/riders-template.xlsx
@@ -3577,7 +3577,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="C3:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"완료,미완료"</formula1>
+      <formula1>"온라인,오프라인,미완료"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/development/service-ops-api/src/main/resources/templates/excel/riders-template.xlsx
+++ b/development/service-ops-api/src/main/resources/templates/excel/riders-template.xlsx
@@ -529,7 +529,7 @@
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>교육이수 *
-(완료 / 미완료)</t>
+(온라인 / 오프라인 / 미완료)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>온라인</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>온라인</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">

--- a/development/service-ops-api/src/main/resources/templates/excel/riders-template.xlsx
+++ b/development/service-ops-api/src/main/resources/templates/excel/riders-template.xlsx
@@ -9,9 +9,16 @@
   <sheets>
     <sheet name="라이더 등록" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
+  <si>
+    <t>관리구분 (삭제 시 '삭제' 입력)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -498,13 +505,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:E500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" customWidth="true" width="16.0"/>
+    <col min="2" max="2" customWidth="true" width="20.0"/>
+    <col min="3" max="3" customWidth="true" width="16.0"/>
+    <col min="4" max="4" customWidth="true" width="16.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -513,6 +520,7 @@
           <t>※ 필수(*) 항목을 모두 입력하세요. 연락처 형식: 010-XXXX-XXXX. 팀은 시스템에 등록된 팀 이름을 입력하세요.</t>
         </is>
       </c>
+      <c r="E1" s="0"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -538,6 +546,9 @@
 (선택)</t>
         </is>
       </c>
+      <c r="E2" t="s" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">

--- a/development/service-ops-api/src/main/resources/templates/excel/riders-template.xlsx
+++ b/development/service-ops-api/src/main/resources/templates/excel/riders-template.xlsx
@@ -9,16 +9,9 @@
   <sheets>
     <sheet name="라이더 등록" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="1">
-  <si>
-    <t>관리구분 (삭제 시 '삭제' 입력)</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -505,13 +498,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E500"/>
+  <dimension ref="A1:D500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="16.0"/>
-    <col min="2" max="2" customWidth="true" width="20.0"/>
-    <col min="3" max="3" customWidth="true" width="16.0"/>
-    <col min="4" max="4" customWidth="true" width="16.0"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -520,7 +513,6 @@
           <t>※ 필수(*) 항목을 모두 입력하세요. 연락처 형식: 010-XXXX-XXXX. 팀은 시스템에 등록된 팀 이름을 입력하세요.</t>
         </is>
       </c>
-      <c r="E1" s="0"/>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -546,9 +538,6 @@
 (선택)</t>
         </is>
       </c>
-      <c r="E2" t="s" s="0">
-        <v>0</v>
-      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
